--- a/Line Sensor Test/linesensor_arc_data.xlsx
+++ b/Line Sensor Test/linesensor_arc_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uob-my.sharepoint.com/personal/vv21600_bristol_ac_uk/Documents/Year4onedrive/Robotics/group_assessment/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c48cfaa2fe489af5/Documents/GitHub/SEMTM0042_43_Group/Line Sensor Test/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="14" documentId="8_{CC151F03-720E-1546-807B-4A8A1B782D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02E3A22A-73B3-D94C-BEF6-F36E645A7B65}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1400" windowWidth="27640" windowHeight="16680" xr2:uid="{CA8326B2-C35C-8C45-9E21-DF537C19ECFE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{CA8326B2-C35C-8C45-9E21-DF537C19ECFE}"/>
   </bookViews>
   <sheets>
     <sheet name="150x0y" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
   <connection id="1" xr16:uid="{F7682CE2-9F14-9A46-8593-80CFCE4C8158}" name="100x0yF" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr codePage="10000" firstRow="8" sourceFile="/Users/jamesbeavon/Library/CloudStorage/OneDrive-UniversityofBristol/Year4onedrive/Robotics/group_assessment/100x0yF.rtf" tab="0" comma="1">
+    <textPr firstRow="8" sourceFile="/Users/jamesbeavon/Library/CloudStorage/OneDrive-UniversityofBristol/Year4onedrive/Robotics/group_assessment/100x0yF.rtf" tab="0" comma="1">
       <textFields count="4">
         <textField type="skip"/>
         <textField/>
@@ -49,7 +49,7 @@
     </textPr>
   </connection>
   <connection id="2" xr16:uid="{84AEEB18-353B-3642-B1D2-B59E2E87CE38}" name="100x0yL" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr codePage="10000" firstRow="8" sourceFile="/Users/jamesbeavon/Library/CloudStorage/OneDrive-UniversityofBristol/Year4onedrive/Robotics/group_assessment/100x0yL.rtf" tab="0" comma="1">
+    <textPr firstRow="8" sourceFile="/Users/jamesbeavon/Library/CloudStorage/OneDrive-UniversityofBristol/Year4onedrive/Robotics/group_assessment/100x0yL.rtf" tab="0" comma="1">
       <textFields count="4">
         <textField type="skip"/>
         <textField/>
@@ -59,7 +59,7 @@
     </textPr>
   </connection>
   <connection id="3" xr16:uid="{7779F7D0-0761-9945-8BCA-C239233A67C0}" name="110x0yF" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr codePage="10000" firstRow="8" sourceFile="/Users/jamesbeavon/Library/CloudStorage/OneDrive-UniversityofBristol/Year4onedrive/Robotics/group_assessment/110x0yF.rtf" tab="0" comma="1">
+    <textPr firstRow="8" sourceFile="/Users/jamesbeavon/Library/CloudStorage/OneDrive-UniversityofBristol/Year4onedrive/Robotics/group_assessment/110x0yF.rtf" tab="0" comma="1">
       <textFields count="4">
         <textField type="skip"/>
         <textField/>
@@ -69,7 +69,7 @@
     </textPr>
   </connection>
   <connection id="4" xr16:uid="{4A105231-1669-E54F-B345-67060C45CC76}" name="110x0yL" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr codePage="10000" firstRow="8" sourceFile="/Users/jamesbeavon/Library/CloudStorage/OneDrive-UniversityofBristol/Year4onedrive/Robotics/group_assessment/110x0yL.rtf" tab="0" comma="1">
+    <textPr firstRow="8" sourceFile="/Users/jamesbeavon/Library/CloudStorage/OneDrive-UniversityofBristol/Year4onedrive/Robotics/group_assessment/110x0yL.rtf" tab="0" comma="1">
       <textFields count="4">
         <textField type="skip"/>
         <textField/>
@@ -1058,9 +1058,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F489757A-67D7-7F48-AACB-C9EB27663E78}">
   <dimension ref="A1:H252"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -1068,7 +1068,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1088,7 +1088,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>0</v>
       </c>
@@ -1108,7 +1108,7 @@
         <v>14431</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>-0.14000000000000001</v>
       </c>
@@ -1128,7 +1128,7 @@
         <v>14481</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>-0.42</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>14531</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>-3.83</v>
       </c>
@@ -1168,7 +1168,7 @@
         <v>14581</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>-7.1</v>
       </c>
@@ -1188,7 +1188,7 @@
         <v>14631</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>-11.5</v>
       </c>
@@ -1208,7 +1208,7 @@
         <v>14681</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>-14.34</v>
       </c>
@@ -1228,7 +1228,7 @@
         <v>14731</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>-18.45</v>
       </c>
@@ -1248,7 +1248,7 @@
         <v>14781</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>-22.42</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>14831</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>-25.12</v>
       </c>
@@ -1288,7 +1288,7 @@
         <v>14881</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>-29.51</v>
       </c>
@@ -1308,7 +1308,7 @@
         <v>14931</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>-32.200000000000003</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>14981</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>-36.450000000000003</v>
       </c>
@@ -1348,7 +1348,7 @@
         <v>15031</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>-39.28</v>
       </c>
@@ -1368,7 +1368,7 @@
         <v>15081</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>-43.81</v>
       </c>
@@ -1388,7 +1388,7 @@
         <v>15131</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>-46.64</v>
       </c>
@@ -1408,7 +1408,7 @@
         <v>15181</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>-51.3</v>
       </c>
@@ -1428,7 +1428,7 @@
         <v>15232</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>-54.26</v>
       </c>
@@ -1448,7 +1448,7 @@
         <v>15291</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>-58.78</v>
       </c>
@@ -1468,7 +1468,7 @@
         <v>15341</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>-61.6</v>
       </c>
@@ -1488,7 +1488,7 @@
         <v>15391</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>-66.38</v>
       </c>
@@ -1508,7 +1508,7 @@
         <v>15441</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>-69.48</v>
       </c>
@@ -1528,7 +1528,7 @@
         <v>15491</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>-74.12</v>
       </c>
@@ -1548,7 +1548,7 @@
         <v>15541</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>-77.209999999999994</v>
       </c>
@@ -1568,7 +1568,7 @@
         <v>15591</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>-81.84</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>15641</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>-84.93</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>15691</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>-89.83</v>
       </c>
@@ -1628,7 +1628,7 @@
         <v>15741</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>-93.05</v>
       </c>
@@ -1648,7 +1648,7 @@
         <v>15791</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>-97.94</v>
       </c>
@@ -1668,7 +1668,7 @@
         <v>15841</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>-101.15</v>
       </c>
@@ -1688,7 +1688,7 @@
         <v>15891</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>-106.02</v>
       </c>
@@ -1708,7 +1708,7 @@
         <v>15941</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>-109.36</v>
       </c>
@@ -1728,7 +1728,7 @@
         <v>15991</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>-114.09</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>16041</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>-117.42</v>
       </c>
@@ -1768,7 +1768,7 @@
         <v>16091</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>-120.88</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>16141</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>-126</v>
       </c>
@@ -1808,7 +1808,7 @@
         <v>16191</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>-129.44999999999999</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>16241</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>-134.41999999999999</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>16291</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>-137.72</v>
       </c>
@@ -1868,7 +1868,7 @@
         <v>16342</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>-142.94999999999999</v>
       </c>
@@ -1888,7 +1888,7 @@
         <v>16401</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>-146.37</v>
       </c>
@@ -1908,7 +1908,7 @@
         <v>16451</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>-151.57</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>16501</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>-154.97999999999999</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>16551</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>-160.02000000000001</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>16601</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>-163.41999999999999</v>
       </c>
@@ -1988,7 +1988,7 @@
         <v>16651</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>-168.71</v>
       </c>
@@ -2008,7 +2008,7 @@
         <v>16701</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>-172.09</v>
       </c>
@@ -2028,7 +2028,7 @@
         <v>16751</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>-177.22</v>
       </c>
@@ -2048,7 +2048,7 @@
         <v>16801</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>-180.99</v>
       </c>
@@ -2068,7 +2068,7 @@
         <v>16851</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>-186.24</v>
       </c>
@@ -2088,7 +2088,7 @@
         <v>16901</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>-189.72</v>
       </c>
@@ -2108,7 +2108,7 @@
         <v>16951</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>-195.2</v>
       </c>
@@ -2128,7 +2128,7 @@
         <v>17001</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>-198.67</v>
       </c>
@@ -2148,7 +2148,7 @@
         <v>17051</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>-203.85</v>
       </c>
@@ -2168,7 +2168,7 @@
         <v>17101</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>-207.42</v>
       </c>
@@ -2188,7 +2188,7 @@
         <v>17152</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>-212.58</v>
       </c>
@@ -2208,7 +2208,7 @@
         <v>17211</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>-216.13</v>
       </c>
@@ -2228,7 +2228,7 @@
         <v>17261</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>-221.37</v>
       </c>
@@ -2248,7 +2248,7 @@
         <v>17311</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>-225.04</v>
       </c>
@@ -2268,7 +2268,7 @@
         <v>17361</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>-230.25</v>
       </c>
@@ -2288,7 +2288,7 @@
         <v>17411</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>-233.89</v>
       </c>
@@ -2308,7 +2308,7 @@
         <v>17461</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>-239.33</v>
       </c>
@@ -2328,7 +2328,7 @@
         <v>17511</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>-242.93</v>
       </c>
@@ -2348,7 +2348,7 @@
         <v>17561</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>-248.45</v>
       </c>
@@ -2368,7 +2368,7 @@
         <v>17611</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>-251.77</v>
       </c>
@@ -2388,7 +2388,7 @@
         <v>17661</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>-257.12</v>
       </c>
@@ -2408,7 +2408,7 @@
         <v>17711</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>-260.68</v>
       </c>
@@ -2428,7 +2428,7 @@
         <v>17761</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>-264.85000000000002</v>
       </c>
@@ -2448,7 +2448,7 @@
         <v>17811</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>-267.37</v>
       </c>
@@ -2468,7 +2468,7 @@
         <v>17861</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>-270.75</v>
       </c>
@@ -2488,7 +2488,7 @@
         <v>17911</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>-273.24</v>
       </c>
@@ -2508,7 +2508,7 @@
         <v>17961</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>-275.48</v>
       </c>
@@ -2528,7 +2528,7 @@
         <v>18011</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>-279.19</v>
       </c>
@@ -2548,7 +2548,7 @@
         <v>18061</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>-281.66000000000003</v>
       </c>
@@ -2568,7 +2568,7 @@
         <v>18111</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>-285.45999999999998</v>
       </c>
@@ -2588,7 +2588,7 @@
         <v>18161</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>-287.66000000000003</v>
       </c>
@@ -2608,7 +2608,7 @@
         <v>18211</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>-291.06</v>
       </c>
@@ -2628,7 +2628,7 @@
         <v>18262</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>-293.47000000000003</v>
       </c>
@@ -2648,7 +2648,7 @@
         <v>18321</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>-297.07</v>
       </c>
@@ -2668,7 +2668,7 @@
         <v>18371</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>-299.33999999999997</v>
       </c>
@@ -2688,7 +2688,7 @@
         <v>18421</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>-302.89999999999998</v>
       </c>
@@ -2708,7 +2708,7 @@
         <v>18471</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F166">
         <v>232.43</v>
       </c>
@@ -2719,7 +2719,7 @@
         <v>18521</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F168">
         <v>237.05</v>
       </c>
@@ -2730,7 +2730,7 @@
         <v>18571</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F170">
         <v>241.91</v>
       </c>
@@ -2741,7 +2741,7 @@
         <v>18621</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F172">
         <v>246.6</v>
       </c>
@@ -2752,7 +2752,7 @@
         <v>18671</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F174">
         <v>251.25</v>
       </c>
@@ -2763,7 +2763,7 @@
         <v>18721</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F176">
         <v>255.73</v>
       </c>
@@ -2774,7 +2774,7 @@
         <v>18771</v>
       </c>
     </row>
-    <row r="178" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="178" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F178">
         <v>260.43</v>
       </c>
@@ -2785,7 +2785,7 @@
         <v>18821</v>
       </c>
     </row>
-    <row r="180" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="180" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F180">
         <v>264.83999999999997</v>
       </c>
@@ -2796,7 +2796,7 @@
         <v>18871</v>
       </c>
     </row>
-    <row r="182" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="182" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F182">
         <v>269.35000000000002</v>
       </c>
@@ -2807,7 +2807,7 @@
         <v>18921</v>
       </c>
     </row>
-    <row r="184" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="184" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F184">
         <v>273.82</v>
       </c>
@@ -2818,7 +2818,7 @@
         <v>18971</v>
       </c>
     </row>
-    <row r="186" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="186" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F186">
         <v>278.27999999999997</v>
       </c>
@@ -2829,7 +2829,7 @@
         <v>19021</v>
       </c>
     </row>
-    <row r="188" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="188" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F188">
         <v>282.58</v>
       </c>
@@ -2840,7 +2840,7 @@
         <v>19072</v>
       </c>
     </row>
-    <row r="190" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="190" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F190">
         <v>287.87</v>
       </c>
@@ -2851,7 +2851,7 @@
         <v>19131</v>
       </c>
     </row>
-    <row r="192" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="192" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F192">
         <v>292.14</v>
       </c>
@@ -2862,7 +2862,7 @@
         <v>19181</v>
       </c>
     </row>
-    <row r="194" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="194" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F194">
         <v>296.29000000000002</v>
       </c>
@@ -2873,7 +2873,7 @@
         <v>19231</v>
       </c>
     </row>
-    <row r="196" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="196" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F196">
         <v>300.68</v>
       </c>
@@ -2884,7 +2884,7 @@
         <v>19281</v>
       </c>
     </row>
-    <row r="198" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="198" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F198">
         <v>305.08</v>
       </c>
@@ -2895,7 +2895,7 @@
         <v>19331</v>
       </c>
     </row>
-    <row r="200" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="200" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F200">
         <v>309.24</v>
       </c>
@@ -2906,7 +2906,7 @@
         <v>19381</v>
       </c>
     </row>
-    <row r="202" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="202" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F202">
         <v>313.55</v>
       </c>
@@ -2917,7 +2917,7 @@
         <v>19431</v>
       </c>
     </row>
-    <row r="204" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="204" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F204">
         <v>318.14</v>
       </c>
@@ -2928,7 +2928,7 @@
         <v>19481</v>
       </c>
     </row>
-    <row r="206" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="206" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F206">
         <v>322.64</v>
       </c>
@@ -2939,7 +2939,7 @@
         <v>19531</v>
       </c>
     </row>
-    <row r="208" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="208" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F208">
         <v>327.17</v>
       </c>
@@ -2950,7 +2950,7 @@
         <v>19581</v>
       </c>
     </row>
-    <row r="210" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="210" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F210">
         <v>-323.47000000000003</v>
       </c>
@@ -2961,7 +2961,7 @@
         <v>19631</v>
       </c>
     </row>
-    <row r="212" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="212" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F212">
         <v>-319.08999999999997</v>
       </c>
@@ -2972,7 +2972,7 @@
         <v>19681</v>
       </c>
     </row>
-    <row r="214" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="214" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F214">
         <v>-315.06</v>
       </c>
@@ -2983,7 +2983,7 @@
         <v>19731</v>
       </c>
     </row>
-    <row r="216" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="216" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F216">
         <v>-313.7</v>
       </c>
@@ -2994,7 +2994,7 @@
         <v>19781</v>
       </c>
     </row>
-    <row r="218" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="218" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F218">
         <v>-313.57</v>
       </c>
@@ -3005,7 +3005,7 @@
         <v>19831</v>
       </c>
     </row>
-    <row r="220" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="220" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F220">
         <v>-313.57</v>
       </c>
@@ -3016,7 +3016,7 @@
         <v>19881</v>
       </c>
     </row>
-    <row r="222" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="222" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F222">
         <v>-313.57</v>
       </c>
@@ -3027,7 +3027,7 @@
         <v>19931</v>
       </c>
     </row>
-    <row r="224" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="224" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F224">
         <v>-313.57</v>
       </c>
@@ -3038,7 +3038,7 @@
         <v>19981</v>
       </c>
     </row>
-    <row r="226" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="226" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F226">
         <v>-313.57</v>
       </c>
@@ -3049,7 +3049,7 @@
         <v>20031</v>
       </c>
     </row>
-    <row r="228" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="228" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F228">
         <v>-313.57</v>
       </c>
@@ -3060,7 +3060,7 @@
         <v>20081</v>
       </c>
     </row>
-    <row r="230" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="230" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F230">
         <v>-313.57</v>
       </c>
@@ -3071,7 +3071,7 @@
         <v>20131</v>
       </c>
     </row>
-    <row r="232" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="232" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F232">
         <v>-313.57</v>
       </c>
@@ -3082,7 +3082,7 @@
         <v>20182</v>
       </c>
     </row>
-    <row r="234" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="234" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F234">
         <v>-313.57</v>
       </c>
@@ -3093,7 +3093,7 @@
         <v>20241</v>
       </c>
     </row>
-    <row r="236" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="236" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F236">
         <v>-313.57</v>
       </c>
@@ -3104,7 +3104,7 @@
         <v>20291</v>
       </c>
     </row>
-    <row r="238" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="238" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F238">
         <v>-313.57</v>
       </c>
@@ -3115,7 +3115,7 @@
         <v>20341</v>
       </c>
     </row>
-    <row r="240" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="240" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F240">
         <v>-313.57</v>
       </c>
@@ -3126,7 +3126,7 @@
         <v>20391</v>
       </c>
     </row>
-    <row r="242" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="242" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F242">
         <v>-313.57</v>
       </c>
@@ -3137,7 +3137,7 @@
         <v>20441</v>
       </c>
     </row>
-    <row r="244" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="244" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F244">
         <v>-313.57</v>
       </c>
@@ -3148,7 +3148,7 @@
         <v>20491</v>
       </c>
     </row>
-    <row r="246" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="246" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F246">
         <v>-313.57</v>
       </c>
@@ -3159,7 +3159,7 @@
         <v>20541</v>
       </c>
     </row>
-    <row r="248" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="248" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F248">
         <v>-313.57</v>
       </c>
@@ -3170,7 +3170,7 @@
         <v>20591</v>
       </c>
     </row>
-    <row r="250" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="250" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F250">
         <v>-313.57</v>
       </c>
@@ -3181,7 +3181,7 @@
         <v>20641</v>
       </c>
     </row>
-    <row r="252" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="252" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F252">
         <v>-313.57</v>
       </c>
@@ -3200,16 +3200,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1747BED3-AD59-1240-988A-FE1F30E4DD56}">
   <dimension ref="A1:H218"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.19921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -3217,7 +3217,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -3237,7 +3237,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>0</v>
       </c>
@@ -3257,7 +3257,7 @@
         <v>14441</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>-0.42</v>
       </c>
@@ -3277,7 +3277,7 @@
         <v>14491</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>-0.56000000000000005</v>
       </c>
@@ -3297,7 +3297,7 @@
         <v>14541</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>-2.13</v>
       </c>
@@ -3317,7 +3317,7 @@
         <v>14592</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>-5.53</v>
       </c>
@@ -3337,7 +3337,7 @@
         <v>14651</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>-10.08</v>
       </c>
@@ -3357,7 +3357,7 @@
         <v>14701</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>-12.92</v>
       </c>
@@ -3377,7 +3377,7 @@
         <v>14751</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>-17.170000000000002</v>
       </c>
@@ -3397,7 +3397,7 @@
         <v>14801</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>-19.87</v>
       </c>
@@ -3417,7 +3417,7 @@
         <v>14851</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>-24.26</v>
       </c>
@@ -3437,7 +3437,7 @@
         <v>14901</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>-27.1</v>
       </c>
@@ -3457,7 +3457,7 @@
         <v>14951</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>-31.35</v>
       </c>
@@ -3477,7 +3477,7 @@
         <v>15001</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>-34.18</v>
       </c>
@@ -3497,7 +3497,7 @@
         <v>15051</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>-38.57</v>
       </c>
@@ -3517,7 +3517,7 @@
         <v>15101</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>-41.4</v>
       </c>
@@ -3537,7 +3537,7 @@
         <v>15151</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>-46.21</v>
       </c>
@@ -3557,7 +3557,7 @@
         <v>15201</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>-49.04</v>
       </c>
@@ -3577,7 +3577,7 @@
         <v>15251</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>-53.56</v>
       </c>
@@ -3597,7 +3597,7 @@
         <v>15301</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>-56.66</v>
       </c>
@@ -3617,7 +3617,7 @@
         <v>15351</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>-61.32</v>
       </c>
@@ -3637,7 +3637,7 @@
         <v>15401</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>-64.28</v>
       </c>
@@ -3657,7 +3657,7 @@
         <v>15451</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>-68.92</v>
       </c>
@@ -3677,7 +3677,7 @@
         <v>15501</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>-72.150000000000006</v>
       </c>
@@ -3697,7 +3697,7 @@
         <v>15551</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>-75.39</v>
       </c>
@@ -3717,7 +3717,7 @@
         <v>15601</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>-80.16</v>
       </c>
@@ -3737,7 +3737,7 @@
         <v>15651</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>-83.25</v>
       </c>
@@ -3757,7 +3757,7 @@
         <v>15702</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>-88.15</v>
       </c>
@@ -3777,7 +3777,7 @@
         <v>15761</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>-91.37</v>
       </c>
@@ -3797,7 +3797,7 @@
         <v>15811</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>-96.12</v>
       </c>
@@ -3817,7 +3817,7 @@
         <v>15861</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>-99.47</v>
       </c>
@@ -3837,7 +3837,7 @@
         <v>15911</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>-104.49</v>
       </c>
@@ -3857,7 +3857,7 @@
         <v>15961</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>-107.68</v>
       </c>
@@ -3877,7 +3877,7 @@
         <v>16011</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>-112.68</v>
       </c>
@@ -3897,7 +3897,7 @@
         <v>16061</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>-116.01</v>
       </c>
@@ -3917,7 +3917,7 @@
         <v>16111</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>-120.99</v>
       </c>
@@ -3937,7 +3937,7 @@
         <v>16161</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>-124.44</v>
       </c>
@@ -3957,7 +3957,7 @@
         <v>16211</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>-129.41</v>
       </c>
@@ -3977,7 +3977,7 @@
         <v>16261</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>-132.85</v>
       </c>
@@ -3997,7 +3997,7 @@
         <v>16311</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>-137.80000000000001</v>
       </c>
@@ -4017,7 +4017,7 @@
         <v>16361</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>-141.1</v>
       </c>
@@ -4037,7 +4037,7 @@
         <v>16411</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>-146.31</v>
       </c>
@@ -4057,7 +4057,7 @@
         <v>16461</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>-149.72999999999999</v>
       </c>
@@ -4077,7 +4077,7 @@
         <v>16512</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>-154.78</v>
       </c>
@@ -4097,7 +4097,7 @@
         <v>16571</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>-158.31</v>
       </c>
@@ -4117,7 +4117,7 @@
         <v>16621</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>-163.61000000000001</v>
       </c>
@@ -4137,7 +4137,7 @@
         <v>16671</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>-166.99</v>
       </c>
@@ -4157,7 +4157,7 @@
         <v>16721</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>-172.26</v>
       </c>
@@ -4177,7 +4177,7 @@
         <v>16771</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>-175.77</v>
       </c>
@@ -4197,7 +4197,7 @@
         <v>16821</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>-181.01</v>
       </c>
@@ -4217,7 +4217,7 @@
         <v>16871</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>-184.49</v>
       </c>
@@ -4237,7 +4237,7 @@
         <v>16921</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>-189.84</v>
       </c>
@@ -4257,7 +4257,7 @@
         <v>16971</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>-193.58</v>
       </c>
@@ -4277,7 +4277,7 @@
         <v>17021</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>-198.76</v>
       </c>
@@ -4297,7 +4297,7 @@
         <v>17071</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>-202.34</v>
       </c>
@@ -4317,7 +4317,7 @@
         <v>17121</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>-207.62</v>
       </c>
@@ -4337,7 +4337,7 @@
         <v>17171</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>-211.05</v>
       </c>
@@ -4357,7 +4357,7 @@
         <v>17221</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>-216.43</v>
       </c>
@@ -4377,7 +4377,7 @@
         <v>17271</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>-219.96</v>
       </c>
@@ -4397,7 +4397,7 @@
         <v>17321</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>-223.49</v>
       </c>
@@ -4417,7 +4417,7 @@
         <v>17371</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>-228.95</v>
       </c>
@@ -4437,7 +4437,7 @@
         <v>17421</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>-232.58</v>
       </c>
@@ -4457,7 +4457,7 @@
         <v>17471</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>-237.87</v>
       </c>
@@ -4477,7 +4477,7 @@
         <v>17521</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>-241.6</v>
       </c>
@@ -4497,7 +4497,7 @@
         <v>17571</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>-246.99</v>
       </c>
@@ -4517,7 +4517,7 @@
         <v>17622</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>-250.56</v>
       </c>
@@ -4537,7 +4537,7 @@
         <v>17681</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>-255.77</v>
       </c>
@@ -4557,7 +4557,7 @@
         <v>17731</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>-259.56</v>
       </c>
@@ -4577,7 +4577,7 @@
         <v>17781</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>-264.47000000000003</v>
       </c>
@@ -4597,7 +4597,7 @@
         <v>17831</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>-266.73</v>
       </c>
@@ -4617,7 +4617,7 @@
         <v>17881</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>-270.10000000000002</v>
       </c>
@@ -4637,7 +4637,7 @@
         <v>17931</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>-272.08999999999997</v>
       </c>
@@ -4657,7 +4657,7 @@
         <v>17981</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>-275.93</v>
       </c>
@@ -4677,7 +4677,7 @@
         <v>18031</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>-278.39</v>
       </c>
@@ -4697,7 +4697,7 @@
         <v>18081</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>-282.06</v>
       </c>
@@ -4717,7 +4717,7 @@
         <v>18131</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>-284.25</v>
       </c>
@@ -4737,7 +4737,7 @@
         <v>18181</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>-288</v>
       </c>
@@ -4757,7 +4757,7 @@
         <v>18231</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>-290.29000000000002</v>
       </c>
@@ -4777,7 +4777,7 @@
         <v>18281</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>-293.76</v>
       </c>
@@ -4797,7 +4797,7 @@
         <v>18331</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>-296.14999999999998</v>
       </c>
@@ -4817,7 +4817,7 @@
         <v>18381</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>-299.7</v>
       </c>
@@ -4837,7 +4837,7 @@
         <v>18432</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>-302.06</v>
       </c>
@@ -4857,7 +4857,7 @@
         <v>18491</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F166">
         <v>303.55</v>
       </c>
@@ -4868,7 +4868,7 @@
         <v>18541</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F168">
         <v>307.75</v>
       </c>
@@ -4879,7 +4879,7 @@
         <v>18591</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F170">
         <v>312.08</v>
       </c>
@@ -4890,7 +4890,7 @@
         <v>18641</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F172">
         <v>316.69</v>
       </c>
@@ -4901,7 +4901,7 @@
         <v>18691</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F174">
         <v>321.07</v>
       </c>
@@ -4912,7 +4912,7 @@
         <v>18741</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F176">
         <v>325.47000000000003</v>
       </c>
@@ -4923,7 +4923,7 @@
         <v>18791</v>
       </c>
     </row>
-    <row r="178" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="178" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F178">
         <v>-325.70999999999998</v>
       </c>
@@ -4934,7 +4934,7 @@
         <v>18841</v>
       </c>
     </row>
-    <row r="180" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="180" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F180">
         <v>-322.95</v>
       </c>
@@ -4945,7 +4945,7 @@
         <v>18891</v>
       </c>
     </row>
-    <row r="182" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="182" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F182">
         <v>-322.56</v>
       </c>
@@ -4956,7 +4956,7 @@
         <v>18941</v>
       </c>
     </row>
-    <row r="184" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="184" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F184">
         <v>-322.56</v>
       </c>
@@ -4967,7 +4967,7 @@
         <v>18991</v>
       </c>
     </row>
-    <row r="186" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="186" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F186">
         <v>-322.56</v>
       </c>
@@ -4978,7 +4978,7 @@
         <v>19041</v>
       </c>
     </row>
-    <row r="188" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="188" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F188">
         <v>-322.56</v>
       </c>
@@ -4989,7 +4989,7 @@
         <v>19091</v>
       </c>
     </row>
-    <row r="190" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="190" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F190">
         <v>-322.56</v>
       </c>
@@ -5000,7 +5000,7 @@
         <v>19141</v>
       </c>
     </row>
-    <row r="192" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="192" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F192">
         <v>-322.56</v>
       </c>
@@ -5011,7 +5011,7 @@
         <v>19191</v>
       </c>
     </row>
-    <row r="194" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="194" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F194">
         <v>-322.56</v>
       </c>
@@ -5022,7 +5022,7 @@
         <v>19241</v>
       </c>
     </row>
-    <row r="196" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="196" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F196">
         <v>-322.56</v>
       </c>
@@ -5033,7 +5033,7 @@
         <v>19291</v>
       </c>
     </row>
-    <row r="198" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="198" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F198">
         <v>-322.56</v>
       </c>
@@ -5044,7 +5044,7 @@
         <v>19341</v>
       </c>
     </row>
-    <row r="200" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="200" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F200">
         <v>-322.56</v>
       </c>
@@ -5055,7 +5055,7 @@
         <v>19391</v>
       </c>
     </row>
-    <row r="202" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="202" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F202">
         <v>-322.56</v>
       </c>
@@ -5066,7 +5066,7 @@
         <v>19441</v>
       </c>
     </row>
-    <row r="204" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="204" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F204">
         <v>-322.56</v>
       </c>
@@ -5077,7 +5077,7 @@
         <v>19491</v>
       </c>
     </row>
-    <row r="206" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="206" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F206">
         <v>-322.56</v>
       </c>
@@ -5088,7 +5088,7 @@
         <v>19542</v>
       </c>
     </row>
-    <row r="208" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="208" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F208">
         <v>-322.56</v>
       </c>
@@ -5099,7 +5099,7 @@
         <v>19601</v>
       </c>
     </row>
-    <row r="210" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="210" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F210">
         <v>-322.56</v>
       </c>
@@ -5110,7 +5110,7 @@
         <v>19651</v>
       </c>
     </row>
-    <row r="212" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="212" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F212">
         <v>-322.56</v>
       </c>
@@ -5121,7 +5121,7 @@
         <v>19701</v>
       </c>
     </row>
-    <row r="214" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="214" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F214">
         <v>-322.56</v>
       </c>
@@ -5132,7 +5132,7 @@
         <v>19751</v>
       </c>
     </row>
-    <row r="216" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="216" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F216">
         <v>-322.56</v>
       </c>
@@ -5143,7 +5143,7 @@
         <v>19801</v>
       </c>
     </row>
-    <row r="218" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="218" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F218">
         <v>-322.56</v>
       </c>
@@ -5162,17 +5162,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1997D4F-AFB2-F14C-B4DA-9BFB77B6B443}">
   <dimension ref="A1:H224"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.19921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -5180,7 +5180,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -5200,7 +5200,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>0</v>
       </c>
@@ -5220,7 +5220,7 @@
         <v>14431</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>-0.42</v>
       </c>
@@ -5240,7 +5240,7 @@
         <v>14481</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>-0.42</v>
       </c>
@@ -5260,7 +5260,7 @@
         <v>14531</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>-0.99</v>
       </c>
@@ -5280,7 +5280,7 @@
         <v>14581</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>-4.54</v>
       </c>
@@ -5300,7 +5300,7 @@
         <v>14631</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>-9.3699999999999992</v>
       </c>
@@ -5320,7 +5320,7 @@
         <v>14681</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>-12.07</v>
       </c>
@@ -5340,7 +5340,7 @@
         <v>14731</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>-16.47</v>
       </c>
@@ -5360,7 +5360,7 @@
         <v>14781</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>-19.03</v>
       </c>
@@ -5380,7 +5380,7 @@
         <v>14831</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>-23</v>
       </c>
@@ -5400,7 +5400,7 @@
         <v>14881</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>-25.98</v>
       </c>
@@ -5420,7 +5420,7 @@
         <v>14931</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>-30.38</v>
       </c>
@@ -5440,7 +5440,7 @@
         <v>14981</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>-33.36</v>
       </c>
@@ -5460,7 +5460,7 @@
         <v>15031</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>-37.61</v>
       </c>
@@ -5480,7 +5480,7 @@
         <v>15081</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>-40.729999999999997</v>
       </c>
@@ -5500,7 +5500,7 @@
         <v>15131</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>-45.26</v>
       </c>
@@ -5520,7 +5520,7 @@
         <v>15181</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>-48.24</v>
       </c>
@@ -5540,7 +5540,7 @@
         <v>15232</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>-52.91</v>
       </c>
@@ -5560,7 +5560,7 @@
         <v>15291</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>-55.88</v>
       </c>
@@ -5580,7 +5580,7 @@
         <v>15341</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>-60.54</v>
       </c>
@@ -5600,7 +5600,7 @@
         <v>15391</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>-63.5</v>
       </c>
@@ -5620,7 +5620,7 @@
         <v>15441</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>-68.16</v>
       </c>
@@ -5640,7 +5640,7 @@
         <v>15491</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>-71.400000000000006</v>
       </c>
@@ -5660,7 +5660,7 @@
         <v>15541</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>-76.19</v>
       </c>
@@ -5680,7 +5680,7 @@
         <v>15591</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>-79.28</v>
       </c>
@@ -5700,7 +5700,7 @@
         <v>15641</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>-84.06</v>
       </c>
@@ -5720,7 +5720,7 @@
         <v>15691</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>-87.42</v>
       </c>
@@ -5740,7 +5740,7 @@
         <v>15741</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>-92.19</v>
       </c>
@@ -5760,7 +5760,7 @@
         <v>15791</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>-95.41</v>
       </c>
@@ -5780,7 +5780,7 @@
         <v>15841</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>-100.58</v>
       </c>
@@ -5800,7 +5800,7 @@
         <v>15891</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>-103.8</v>
       </c>
@@ -5820,7 +5820,7 @@
         <v>15941</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>-108.68</v>
       </c>
@@ -5840,7 +5840,7 @@
         <v>15991</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>-111.89</v>
       </c>
@@ -5860,7 +5860,7 @@
         <v>16041</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>-116.9</v>
       </c>
@@ -5880,7 +5880,7 @@
         <v>16091</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>-120.09</v>
       </c>
@@ -5900,7 +5900,7 @@
         <v>16141</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>-125.23</v>
       </c>
@@ -5920,7 +5920,7 @@
         <v>16191</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>-128.69</v>
       </c>
@@ -5940,7 +5940,7 @@
         <v>16241</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>-133.53</v>
       </c>
@@ -5960,7 +5960,7 @@
         <v>16291</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>-137.11000000000001</v>
       </c>
@@ -5980,7 +5980,7 @@
         <v>16342</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>-142.35</v>
       </c>
@@ -6000,7 +6000,7 @@
         <v>16401</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>-145.79</v>
       </c>
@@ -6020,7 +6020,7 @@
         <v>16451</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>-150.87</v>
       </c>
@@ -6040,7 +6040,7 @@
         <v>16501</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>-154.43</v>
       </c>
@@ -6060,7 +6060,7 @@
         <v>16551</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>-159.63</v>
       </c>
@@ -6080,7 +6080,7 @@
         <v>16601</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>-163.16999999999999</v>
       </c>
@@ -6100,7 +6100,7 @@
         <v>16651</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>-168.48</v>
       </c>
@@ -6120,7 +6120,7 @@
         <v>16701</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>-172.02</v>
       </c>
@@ -6140,7 +6140,7 @@
         <v>16751</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>-177.16</v>
       </c>
@@ -6160,7 +6160,7 @@
         <v>16801</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>-180.81</v>
       </c>
@@ -6180,7 +6180,7 @@
         <v>16851</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>-186.06</v>
       </c>
@@ -6200,7 +6200,7 @@
         <v>16901</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>-189.55</v>
       </c>
@@ -6220,7 +6220,7 @@
         <v>16951</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>-194.91</v>
       </c>
@@ -6240,7 +6240,7 @@
         <v>17001</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>-198.65</v>
       </c>
@@ -6260,7 +6260,7 @@
         <v>17051</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>-203.85</v>
       </c>
@@ -6280,7 +6280,7 @@
         <v>17101</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>-207.17</v>
       </c>
@@ -6300,7 +6300,7 @@
         <v>17152</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>-212.74</v>
       </c>
@@ -6320,7 +6320,7 @@
         <v>17211</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>-216.44</v>
       </c>
@@ -6340,7 +6340,7 @@
         <v>17261</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>-221.71</v>
       </c>
@@ -6360,7 +6360,7 @@
         <v>17311</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>-225.38</v>
       </c>
@@ -6380,7 +6380,7 @@
         <v>17361</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>-230.74</v>
       </c>
@@ -6400,7 +6400,7 @@
         <v>17411</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>-234.26</v>
       </c>
@@ -6420,7 +6420,7 @@
         <v>17461</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>-237.89</v>
       </c>
@@ -6440,7 +6440,7 @@
         <v>17511</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>-243.45</v>
       </c>
@@ -6460,7 +6460,7 @@
         <v>17561</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>-247.06</v>
       </c>
@@ -6480,7 +6480,7 @@
         <v>17611</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>-252.45</v>
       </c>
@@ -6500,7 +6500,7 @@
         <v>17661</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>-256.16000000000003</v>
       </c>
@@ -6520,7 +6520,7 @@
         <v>17711</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>-261.51</v>
       </c>
@@ -6540,7 +6540,7 @@
         <v>17761</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>-265.18</v>
       </c>
@@ -6560,7 +6560,7 @@
         <v>17811</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>-268.83999999999997</v>
       </c>
@@ -6580,7 +6580,7 @@
         <v>17861</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>-271.10000000000002</v>
       </c>
@@ -6600,7 +6600,7 @@
         <v>17911</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>-274.35000000000002</v>
       </c>
@@ -6620,7 +6620,7 @@
         <v>17961</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>-276.7</v>
       </c>
@@ -6640,7 +6640,7 @@
         <v>18011</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>-280.41000000000003</v>
       </c>
@@ -6660,7 +6660,7 @@
         <v>18061</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>-282.75</v>
       </c>
@@ -6680,7 +6680,7 @@
         <v>18111</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>-286.3</v>
       </c>
@@ -6700,7 +6700,7 @@
         <v>18161</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>-288.61</v>
       </c>
@@ -6720,7 +6720,7 @@
         <v>18211</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>-292.13</v>
       </c>
@@ -6740,7 +6740,7 @@
         <v>18262</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>-294.55</v>
       </c>
@@ -6760,7 +6760,7 @@
         <v>18321</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>-298.14</v>
       </c>
@@ -6780,7 +6780,7 @@
         <v>18371</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>-300.41000000000003</v>
       </c>
@@ -6800,7 +6800,7 @@
         <v>18421</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>-304.08999999999997</v>
       </c>
@@ -6820,7 +6820,7 @@
         <v>18471</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F166">
         <v>285.63</v>
       </c>
@@ -6831,7 +6831,7 @@
         <v>18521</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F168">
         <v>290.3</v>
       </c>
@@ -6842,7 +6842,7 @@
         <v>18571</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F170">
         <v>294.82</v>
       </c>
@@ -6853,7 +6853,7 @@
         <v>18621</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F172">
         <v>299.19</v>
       </c>
@@ -6864,7 +6864,7 @@
         <v>18671</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F174">
         <v>303.68</v>
       </c>
@@ -6875,7 +6875,7 @@
         <v>18721</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F176">
         <v>308.02</v>
       </c>
@@ -6886,7 +6886,7 @@
         <v>18771</v>
       </c>
     </row>
-    <row r="178" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="178" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F178">
         <v>312.49</v>
       </c>
@@ -6897,7 +6897,7 @@
         <v>18821</v>
       </c>
     </row>
-    <row r="180" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="180" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F180">
         <v>317.08</v>
       </c>
@@ -6908,7 +6908,7 @@
         <v>18871</v>
       </c>
     </row>
-    <row r="182" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="182" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F182">
         <v>321.55</v>
       </c>
@@ -6919,7 +6919,7 @@
         <v>18921</v>
       </c>
     </row>
-    <row r="184" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="184" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F184">
         <v>325.77</v>
       </c>
@@ -6930,7 +6930,7 @@
         <v>18971</v>
       </c>
     </row>
-    <row r="186" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="186" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F186">
         <v>-325.75</v>
       </c>
@@ -6941,7 +6941,7 @@
         <v>19021</v>
       </c>
     </row>
-    <row r="188" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="188" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F188">
         <v>-324.08</v>
       </c>
@@ -6952,7 +6952,7 @@
         <v>19072</v>
       </c>
     </row>
-    <row r="190" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="190" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F190">
         <v>-323.82</v>
       </c>
@@ -6963,7 +6963,7 @@
         <v>19131</v>
       </c>
     </row>
-    <row r="192" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="192" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F192">
         <v>-323.82</v>
       </c>
@@ -6974,7 +6974,7 @@
         <v>19181</v>
       </c>
     </row>
-    <row r="194" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="194" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F194">
         <v>-323.82</v>
       </c>
@@ -6985,7 +6985,7 @@
         <v>19231</v>
       </c>
     </row>
-    <row r="196" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="196" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F196">
         <v>-323.82</v>
       </c>
@@ -6996,7 +6996,7 @@
         <v>19281</v>
       </c>
     </row>
-    <row r="198" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="198" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F198">
         <v>-323.82</v>
       </c>
@@ -7007,7 +7007,7 @@
         <v>19331</v>
       </c>
     </row>
-    <row r="200" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="200" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F200">
         <v>-323.82</v>
       </c>
@@ -7018,7 +7018,7 @@
         <v>19381</v>
       </c>
     </row>
-    <row r="202" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="202" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F202">
         <v>-323.82</v>
       </c>
@@ -7029,7 +7029,7 @@
         <v>19431</v>
       </c>
     </row>
-    <row r="204" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="204" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F204">
         <v>-323.82</v>
       </c>
@@ -7040,7 +7040,7 @@
         <v>19481</v>
       </c>
     </row>
-    <row r="206" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="206" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F206">
         <v>-323.82</v>
       </c>
@@ -7051,7 +7051,7 @@
         <v>19531</v>
       </c>
     </row>
-    <row r="208" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="208" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F208">
         <v>-323.82</v>
       </c>
@@ -7062,7 +7062,7 @@
         <v>19581</v>
       </c>
     </row>
-    <row r="210" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="210" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F210">
         <v>-323.82</v>
       </c>
@@ -7073,7 +7073,7 @@
         <v>19631</v>
       </c>
     </row>
-    <row r="212" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="212" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F212">
         <v>-323.82</v>
       </c>
@@ -7084,7 +7084,7 @@
         <v>19681</v>
       </c>
     </row>
-    <row r="214" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="214" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F214">
         <v>-323.82</v>
       </c>
@@ -7095,7 +7095,7 @@
         <v>19731</v>
       </c>
     </row>
-    <row r="216" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="216" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F216">
         <v>-323.82</v>
       </c>
@@ -7106,7 +7106,7 @@
         <v>19781</v>
       </c>
     </row>
-    <row r="218" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="218" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F218">
         <v>-323.82</v>
       </c>
@@ -7117,7 +7117,7 @@
         <v>19831</v>
       </c>
     </row>
-    <row r="220" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="220" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F220">
         <v>-323.82</v>
       </c>
@@ -7128,7 +7128,7 @@
         <v>19881</v>
       </c>
     </row>
-    <row r="222" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="222" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F222">
         <v>-323.82</v>
       </c>
@@ -7139,7 +7139,7 @@
         <v>19931</v>
       </c>
     </row>
-    <row r="224" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="224" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F224">
         <v>-323.82</v>
       </c>
@@ -7158,16 +7158,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C164AF9F-2AE5-F34D-8D19-C5A0F833CCA6}">
   <dimension ref="A1:H220"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.19921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -7175,7 +7175,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -7195,7 +7195,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>0</v>
       </c>
@@ -7215,7 +7215,7 @@
         <v>14431</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>0</v>
       </c>
@@ -7235,7 +7235,7 @@
         <v>14481</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>0</v>
       </c>
@@ -7255,7 +7255,7 @@
         <v>14531</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>-1.42</v>
       </c>
@@ -7275,7 +7275,7 @@
         <v>14581</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>-4.97</v>
       </c>
@@ -7295,7 +7295,7 @@
         <v>14631</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>-9.51</v>
       </c>
@@ -7315,7 +7315,7 @@
         <v>14681</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>-12.35</v>
       </c>
@@ -7335,7 +7335,7 @@
         <v>14731</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>-16.47</v>
       </c>
@@ -7355,7 +7355,7 @@
         <v>14781</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>-19.309999999999999</v>
       </c>
@@ -7375,7 +7375,7 @@
         <v>14831</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>-23.57</v>
       </c>
@@ -7395,7 +7395,7 @@
         <v>14881</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>-26.41</v>
       </c>
@@ -7415,7 +7415,7 @@
         <v>14931</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>-30.8</v>
       </c>
@@ -7435,7 +7435,7 @@
         <v>14981</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>-33.5</v>
       </c>
@@ -7455,7 +7455,7 @@
         <v>15031</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>-38.03</v>
       </c>
@@ -7475,7 +7475,7 @@
         <v>15081</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>-41.01</v>
       </c>
@@ -7495,7 +7495,7 @@
         <v>15131</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>-45.68</v>
       </c>
@@ -7515,7 +7515,7 @@
         <v>15181</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>-48.51</v>
       </c>
@@ -7535,7 +7535,7 @@
         <v>15232</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>-52.89</v>
       </c>
@@ -7555,7 +7555,7 @@
         <v>15291</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>-56</v>
       </c>
@@ -7575,7 +7575,7 @@
         <v>15341</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>-60.38</v>
       </c>
@@ -7595,7 +7595,7 @@
         <v>15391</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>-63.76</v>
       </c>
@@ -7615,7 +7615,7 @@
         <v>15441</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>-68.42</v>
       </c>
@@ -7635,7 +7635,7 @@
         <v>15491</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>-71.66</v>
       </c>
@@ -7655,7 +7655,7 @@
         <v>15541</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>-76.3</v>
       </c>
@@ -7675,7 +7675,7 @@
         <v>15591</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>-79.39</v>
       </c>
@@ -7695,7 +7695,7 @@
         <v>15641</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>-84.17</v>
       </c>
@@ -7715,7 +7715,7 @@
         <v>15691</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>-87.26</v>
       </c>
@@ -7735,7 +7735,7 @@
         <v>15741</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>-92.17</v>
       </c>
@@ -7755,7 +7755,7 @@
         <v>15791</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>-95.39</v>
       </c>
@@ -7775,7 +7775,7 @@
         <v>15841</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>-100.42</v>
       </c>
@@ -7795,7 +7795,7 @@
         <v>15891</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>-103.64</v>
       </c>
@@ -7815,7 +7815,7 @@
         <v>15941</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>-108.79</v>
       </c>
@@ -7835,7 +7835,7 @@
         <v>15991</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>-112</v>
       </c>
@@ -7855,7 +7855,7 @@
         <v>16041</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>-116.86</v>
       </c>
@@ -7875,7 +7875,7 @@
         <v>16091</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>-120.19</v>
       </c>
@@ -7895,7 +7895,7 @@
         <v>16141</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>-125.32</v>
       </c>
@@ -7915,7 +7915,7 @@
         <v>16191</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>-128.78</v>
       </c>
@@ -7935,7 +7935,7 @@
         <v>16241</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>-133.75</v>
       </c>
@@ -7955,7 +7955,7 @@
         <v>16291</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>-137.05000000000001</v>
       </c>
@@ -7975,7 +7975,7 @@
         <v>16342</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>-142.41999999999999</v>
       </c>
@@ -7995,7 +7995,7 @@
         <v>16401</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>-145.85</v>
       </c>
@@ -8015,7 +8015,7 @@
         <v>16451</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>-150.78</v>
       </c>
@@ -8035,7 +8035,7 @@
         <v>16501</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>-154.33000000000001</v>
       </c>
@@ -8055,7 +8055,7 @@
         <v>16551</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>-159.52000000000001</v>
       </c>
@@ -8075,7 +8075,7 @@
         <v>16601</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>-162.91999999999999</v>
       </c>
@@ -8095,7 +8095,7 @@
         <v>16651</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>-168.08</v>
       </c>
@@ -8115,7 +8115,7 @@
         <v>16701</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>-171.6</v>
       </c>
@@ -8135,7 +8135,7 @@
         <v>16751</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>-176.74</v>
       </c>
@@ -8155,7 +8155,7 @@
         <v>16801</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>-180.25</v>
       </c>
@@ -8175,7 +8175,7 @@
         <v>16851</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>-185.49</v>
       </c>
@@ -8195,7 +8195,7 @@
         <v>16901</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>-188.98</v>
       </c>
@@ -8215,7 +8215,7 @@
         <v>16951</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>-194.46</v>
       </c>
@@ -8235,7 +8235,7 @@
         <v>17001</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>-197.93</v>
       </c>
@@ -8255,7 +8255,7 @@
         <v>17051</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>-203.25</v>
       </c>
@@ -8275,7 +8275,7 @@
         <v>17101</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>-206.7</v>
       </c>
@@ -8295,7 +8295,7 @@
         <v>17152</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>-212.25</v>
       </c>
@@ -8315,7 +8315,7 @@
         <v>17211</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>-215.81</v>
       </c>
@@ -8335,7 +8335,7 @@
         <v>17261</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>-221.19</v>
       </c>
@@ -8355,7 +8355,7 @@
         <v>17311</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>-224.72</v>
       </c>
@@ -8375,7 +8375,7 @@
         <v>17361</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>-229.93</v>
       </c>
@@ -8395,7 +8395,7 @@
         <v>17411</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>-233.69</v>
       </c>
@@ -8415,7 +8415,7 @@
         <v>17461</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>-239.12</v>
       </c>
@@ -8435,7 +8435,7 @@
         <v>17511</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>-242.59</v>
       </c>
@@ -8455,7 +8455,7 @@
         <v>17561</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>-247.97</v>
       </c>
@@ -8475,7 +8475,7 @@
         <v>17611</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>-251.68</v>
       </c>
@@ -8495,7 +8495,7 @@
         <v>17661</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>-256.77</v>
       </c>
@@ -8515,7 +8515,7 @@
         <v>17711</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>-260.32</v>
       </c>
@@ -8535,7 +8535,7 @@
         <v>17761</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>-265.5</v>
       </c>
@@ -8555,7 +8555,7 @@
         <v>17811</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>-267.64</v>
       </c>
@@ -8575,7 +8575,7 @@
         <v>17861</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>-271.14</v>
       </c>
@@ -8595,7 +8595,7 @@
         <v>17911</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>-273.14</v>
       </c>
@@ -8615,7 +8615,7 @@
         <v>17961</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>-276.97000000000003</v>
       </c>
@@ -8635,7 +8635,7 @@
         <v>18011</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>-279.43</v>
       </c>
@@ -8655,7 +8655,7 @@
         <v>18061</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>-282.85000000000002</v>
       </c>
@@ -8675,7 +8675,7 @@
         <v>18111</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>-285.29000000000002</v>
       </c>
@@ -8695,7 +8695,7 @@
         <v>18161</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>-288.79000000000002</v>
       </c>
@@ -8715,7 +8715,7 @@
         <v>18211</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>-291.2</v>
       </c>
@@ -8735,7 +8735,7 @@
         <v>18262</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>-294.79000000000002</v>
       </c>
@@ -8755,7 +8755,7 @@
         <v>18321</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>-296.82</v>
       </c>
@@ -8775,7 +8775,7 @@
         <v>18371</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>-300.27</v>
       </c>
@@ -8795,7 +8795,7 @@
         <v>18421</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>-302.63</v>
       </c>
@@ -8815,7 +8815,7 @@
         <v>18471</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F166">
         <v>303.44</v>
       </c>
@@ -8826,7 +8826,7 @@
         <v>18521</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F168">
         <v>307.97000000000003</v>
       </c>
@@ -8837,7 +8837,7 @@
         <v>18571</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F170">
         <v>312.58999999999997</v>
       </c>
@@ -8848,7 +8848,7 @@
         <v>18621</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F172">
         <v>317.17</v>
       </c>
@@ -8859,7 +8859,7 @@
         <v>18671</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F174">
         <v>321.43</v>
       </c>
@@ -8870,7 +8870,7 @@
         <v>18721</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F176">
         <v>325.38</v>
       </c>
@@ -8881,7 +8881,7 @@
         <v>18771</v>
       </c>
     </row>
-    <row r="178" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="178" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F178">
         <v>326.51</v>
       </c>
@@ -8892,7 +8892,7 @@
         <v>18821</v>
       </c>
     </row>
-    <row r="180" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="180" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F180">
         <v>326.76</v>
       </c>
@@ -8903,7 +8903,7 @@
         <v>18871</v>
       </c>
     </row>
-    <row r="182" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="182" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F182">
         <v>-327.62</v>
       </c>
@@ -8914,7 +8914,7 @@
         <v>18921</v>
       </c>
     </row>
-    <row r="184" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="184" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F184">
         <v>-327.49</v>
       </c>
@@ -8925,7 +8925,7 @@
         <v>18971</v>
       </c>
     </row>
-    <row r="186" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="186" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F186">
         <v>-327.49</v>
       </c>
@@ -8936,7 +8936,7 @@
         <v>19021</v>
       </c>
     </row>
-    <row r="188" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="188" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F188">
         <v>-327.49</v>
       </c>
@@ -8947,7 +8947,7 @@
         <v>19072</v>
       </c>
     </row>
-    <row r="190" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="190" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F190">
         <v>-327.49</v>
       </c>
@@ -8958,7 +8958,7 @@
         <v>19131</v>
       </c>
     </row>
-    <row r="192" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="192" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F192">
         <v>-327.49</v>
       </c>
@@ -8969,7 +8969,7 @@
         <v>19181</v>
       </c>
     </row>
-    <row r="194" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="194" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F194">
         <v>-327.49</v>
       </c>
@@ -8980,7 +8980,7 @@
         <v>19231</v>
       </c>
     </row>
-    <row r="196" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="196" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F196">
         <v>-327.49</v>
       </c>
@@ -8991,7 +8991,7 @@
         <v>19281</v>
       </c>
     </row>
-    <row r="198" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="198" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F198">
         <v>-327.49</v>
       </c>
@@ -9002,7 +9002,7 @@
         <v>19331</v>
       </c>
     </row>
-    <row r="200" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="200" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F200">
         <v>-327.49</v>
       </c>
@@ -9013,7 +9013,7 @@
         <v>19381</v>
       </c>
     </row>
-    <row r="202" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="202" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F202">
         <v>-327.49</v>
       </c>
@@ -9024,7 +9024,7 @@
         <v>19431</v>
       </c>
     </row>
-    <row r="204" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="204" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F204">
         <v>-327.49</v>
       </c>
@@ -9035,7 +9035,7 @@
         <v>19481</v>
       </c>
     </row>
-    <row r="206" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="206" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F206">
         <v>-327.49</v>
       </c>
@@ -9046,7 +9046,7 @@
         <v>19531</v>
       </c>
     </row>
-    <row r="208" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="208" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F208">
         <v>-327.49</v>
       </c>
@@ -9057,7 +9057,7 @@
         <v>19581</v>
       </c>
     </row>
-    <row r="210" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="210" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F210">
         <v>-327.49</v>
       </c>
@@ -9068,7 +9068,7 @@
         <v>19631</v>
       </c>
     </row>
-    <row r="212" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="212" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F212">
         <v>-327.49</v>
       </c>
@@ -9079,7 +9079,7 @@
         <v>19681</v>
       </c>
     </row>
-    <row r="214" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="214" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F214">
         <v>-327.49</v>
       </c>
@@ -9090,7 +9090,7 @@
         <v>19731</v>
       </c>
     </row>
-    <row r="216" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="216" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F216">
         <v>-327.49</v>
       </c>
@@ -9101,7 +9101,7 @@
         <v>19781</v>
       </c>
     </row>
-    <row r="218" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="218" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F218">
         <v>-327.49</v>
       </c>
@@ -9112,7 +9112,7 @@
         <v>19831</v>
       </c>
     </row>
-    <row r="220" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="220" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F220">
         <v>-327.49</v>
       </c>
@@ -9131,17 +9131,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B609F38B-03E5-1349-A3FA-E11A4C9E8A19}">
   <dimension ref="A1:H232"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.19921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.19921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -9149,7 +9149,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -9169,7 +9169,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>0</v>
       </c>
@@ -9189,7 +9189,7 @@
         <v>14411</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>-0.42</v>
       </c>
@@ -9209,7 +9209,7 @@
         <v>14461</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>-0.85</v>
       </c>
@@ -9229,7 +9229,7 @@
         <v>14511</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>-1.98</v>
       </c>
@@ -9249,7 +9249,7 @@
         <v>14561</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>-5.68</v>
       </c>
@@ -9269,7 +9269,7 @@
         <v>14611</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>-10.37</v>
       </c>
@@ -9289,7 +9289,7 @@
         <v>14661</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>-13.35</v>
       </c>
@@ -9309,7 +9309,7 @@
         <v>14711</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>-17.329999999999998</v>
       </c>
@@ -9329,7 +9329,7 @@
         <v>14761</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>-19.89</v>
       </c>
@@ -9349,7 +9349,7 @@
         <v>14811</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>-24.29</v>
       </c>
@@ -9369,7 +9369,7 @@
         <v>14861</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>-27.13</v>
       </c>
@@ -9389,7 +9389,7 @@
         <v>14911</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>-31.53</v>
       </c>
@@ -9409,7 +9409,7 @@
         <v>14961</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>-34.51</v>
       </c>
@@ -9429,7 +9429,7 @@
         <v>15011</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>-38.9</v>
       </c>
@@ -9449,7 +9449,7 @@
         <v>15062</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>-41.88</v>
       </c>
@@ -9469,7 +9469,7 @@
         <v>15121</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>-46.27</v>
       </c>
@@ -9489,7 +9489,7 @@
         <v>15171</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>-49.39</v>
       </c>
@@ -9509,7 +9509,7 @@
         <v>15221</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>-53.91</v>
       </c>
@@ -9529,7 +9529,7 @@
         <v>15271</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>-57.03</v>
       </c>
@@ -9549,7 +9549,7 @@
         <v>15321</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>-61.69</v>
       </c>
@@ -9569,7 +9569,7 @@
         <v>15371</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>-64.650000000000006</v>
       </c>
@@ -9589,7 +9589,7 @@
         <v>15421</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>-69.45</v>
       </c>
@@ -9609,7 +9609,7 @@
         <v>15471</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>-72.55</v>
       </c>
@@ -9629,7 +9629,7 @@
         <v>15521</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>-77.06</v>
       </c>
@@ -9649,7 +9649,7 @@
         <v>15571</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>-80.44</v>
       </c>
@@ -9669,7 +9669,7 @@
         <v>15621</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>-85.08</v>
       </c>
@@ -9689,7 +9689,7 @@
         <v>15671</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>-88.17</v>
       </c>
@@ -9709,7 +9709,7 @@
         <v>15721</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>-92.94</v>
       </c>
@@ -9729,7 +9729,7 @@
         <v>15771</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>-96.17</v>
       </c>
@@ -9749,7 +9749,7 @@
         <v>15821</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>-101.07</v>
       </c>
@@ -9769,7 +9769,7 @@
         <v>15872</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>-104.42</v>
       </c>
@@ -9789,7 +9789,7 @@
         <v>15931</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>-109.31</v>
       </c>
@@ -9809,7 +9809,7 @@
         <v>15981</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>-112.65</v>
       </c>
@@ -9829,7 +9829,7 @@
         <v>16031</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>-117.66</v>
       </c>
@@ -9849,7 +9849,7 @@
         <v>16081</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>-121.13</v>
       </c>
@@ -9869,7 +9869,7 @@
         <v>16131</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>-126.13</v>
       </c>
@@ -9889,7 +9889,7 @@
         <v>16181</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>-129.44999999999999</v>
       </c>
@@ -9909,7 +9909,7 @@
         <v>16231</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>-134.43</v>
       </c>
@@ -9929,7 +9929,7 @@
         <v>16281</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>-137.88</v>
       </c>
@@ -9949,7 +9949,7 @@
         <v>16331</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>-142.97</v>
       </c>
@@ -9969,7 +9969,7 @@
         <v>16381</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>-146.54</v>
       </c>
@@ -9989,7 +9989,7 @@
         <v>16431</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>-151.75</v>
       </c>
@@ -10009,7 +10009,7 @@
         <v>16481</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>-155.16</v>
       </c>
@@ -10029,7 +10029,7 @@
         <v>16531</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>-160.34</v>
       </c>
@@ -10049,7 +10049,7 @@
         <v>16581</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>-163.74</v>
       </c>
@@ -10069,7 +10069,7 @@
         <v>16631</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>-168.89</v>
       </c>
@@ -10089,7 +10089,7 @@
         <v>16681</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>-172.55</v>
       </c>
@@ -10109,7 +10109,7 @@
         <v>16731</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>-176.07</v>
       </c>
@@ -10129,7 +10129,7 @@
         <v>16781</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>-181.33</v>
       </c>
@@ -10149,7 +10149,7 @@
         <v>16831</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>-184.83</v>
       </c>
@@ -10169,7 +10169,7 @@
         <v>16881</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>-190.05</v>
       </c>
@@ -10189,7 +10189,7 @@
         <v>16931</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>-193.8</v>
       </c>
@@ -10209,7 +10209,7 @@
         <v>16982</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>-199</v>
       </c>
@@ -10229,7 +10229,7 @@
         <v>17041</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>-202.45</v>
       </c>
@@ -10249,7 +10249,7 @@
         <v>17091</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>-207.89</v>
       </c>
@@ -10269,7 +10269,7 @@
         <v>17141</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>-211.32</v>
       </c>
@@ -10289,7 +10289,7 @@
         <v>17191</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>-216.71</v>
       </c>
@@ -10309,7 +10309,7 @@
         <v>17241</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>-220.38</v>
       </c>
@@ -10329,7 +10329,7 @@
         <v>17291</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>-225.61</v>
       </c>
@@ -10349,7 +10349,7 @@
         <v>17341</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>-229.25</v>
       </c>
@@ -10369,7 +10369,7 @@
         <v>17391</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>-234.7</v>
       </c>
@@ -10389,7 +10389,7 @@
         <v>17441</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>-238.19</v>
       </c>
@@ -10409,7 +10409,7 @@
         <v>17491</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>-243.71</v>
       </c>
@@ -10429,7 +10429,7 @@
         <v>17541</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>-247.3</v>
       </c>
@@ -10449,7 +10449,7 @@
         <v>17591</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>-252.52</v>
       </c>
@@ -10469,7 +10469,7 @@
         <v>17641</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>-256.08</v>
       </c>
@@ -10489,7 +10489,7 @@
         <v>17691</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>-261.51</v>
       </c>
@@ -10509,7 +10509,7 @@
         <v>17741</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>-264.91000000000003</v>
       </c>
@@ -10529,7 +10529,7 @@
         <v>17792</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>-268.3</v>
       </c>
@@ -10549,7 +10549,7 @@
         <v>17851</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>-270.92</v>
       </c>
@@ -10569,7 +10569,7 @@
         <v>17901</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>-274.27</v>
       </c>
@@ -10589,7 +10589,7 @@
         <v>17951</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>-276.62</v>
       </c>
@@ -10609,7 +10609,7 @@
         <v>18001</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>-280.31</v>
       </c>
@@ -10629,7 +10629,7 @@
         <v>18051</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>-282.63</v>
       </c>
@@ -10649,7 +10649,7 @@
         <v>18101</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>-286.27999999999997</v>
       </c>
@@ -10669,7 +10669,7 @@
         <v>18151</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>-288.58</v>
       </c>
@@ -10689,7 +10689,7 @@
         <v>18201</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>-292.19</v>
       </c>
@@ -10709,7 +10709,7 @@
         <v>18251</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>-294.58</v>
       </c>
@@ -10729,7 +10729,7 @@
         <v>18301</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>-298.02999999999997</v>
       </c>
@@ -10749,7 +10749,7 @@
         <v>18351</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>-300.39</v>
       </c>
@@ -10769,7 +10769,7 @@
         <v>18401</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>-303.89999999999998</v>
       </c>
@@ -10789,7 +10789,7 @@
         <v>18451</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F166">
         <v>255.35</v>
       </c>
@@ -10800,7 +10800,7 @@
         <v>18501</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F168">
         <v>260.16000000000003</v>
       </c>
@@ -10811,7 +10811,7 @@
         <v>18551</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F170">
         <v>264.8</v>
       </c>
@@ -10822,7 +10822,7 @@
         <v>18601</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F172">
         <v>269.68</v>
       </c>
@@ -10833,7 +10833,7 @@
         <v>18651</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F174">
         <v>274.52999999999997</v>
       </c>
@@ -10844,7 +10844,7 @@
         <v>18701</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F176">
         <v>279.20999999999998</v>
       </c>
@@ -10855,7 +10855,7 @@
         <v>18751</v>
       </c>
     </row>
-    <row r="178" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="178" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F178">
         <v>283.99</v>
       </c>
@@ -10866,7 +10866,7 @@
         <v>18801</v>
       </c>
     </row>
-    <row r="180" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="180" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F180">
         <v>288.58999999999997</v>
       </c>
@@ -10877,7 +10877,7 @@
         <v>18851</v>
       </c>
     </row>
-    <row r="182" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="182" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F182">
         <v>293.02</v>
       </c>
@@ -10888,7 +10888,7 @@
         <v>18902</v>
       </c>
     </row>
-    <row r="184" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="184" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F184">
         <v>298.29000000000002</v>
       </c>
@@ -10899,7 +10899,7 @@
         <v>18961</v>
       </c>
     </row>
-    <row r="186" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="186" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F186">
         <v>302.86</v>
       </c>
@@ -10910,7 +10910,7 @@
         <v>19011</v>
       </c>
     </row>
-    <row r="188" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="188" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F188">
         <v>307.10000000000002</v>
       </c>
@@ -10921,7 +10921,7 @@
         <v>19061</v>
       </c>
     </row>
-    <row r="190" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="190" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F190">
         <v>311.41000000000003</v>
       </c>
@@ -10932,7 +10932,7 @@
         <v>19111</v>
       </c>
     </row>
-    <row r="192" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="192" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F192">
         <v>315.05</v>
       </c>
@@ -10943,7 +10943,7 @@
         <v>19161</v>
       </c>
     </row>
-    <row r="194" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="194" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F194">
         <v>317.19</v>
       </c>
@@ -10954,7 +10954,7 @@
         <v>19211</v>
       </c>
     </row>
-    <row r="196" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="196" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F196">
         <v>317.19</v>
       </c>
@@ -10965,7 +10965,7 @@
         <v>19261</v>
       </c>
     </row>
-    <row r="198" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="198" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F198">
         <v>317.19</v>
       </c>
@@ -10976,7 +10976,7 @@
         <v>19311</v>
       </c>
     </row>
-    <row r="200" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="200" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F200">
         <v>317.19</v>
       </c>
@@ -10987,7 +10987,7 @@
         <v>19361</v>
       </c>
     </row>
-    <row r="202" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="202" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F202">
         <v>317.19</v>
       </c>
@@ -10998,7 +10998,7 @@
         <v>19411</v>
       </c>
     </row>
-    <row r="204" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="204" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F204">
         <v>317.19</v>
       </c>
@@ -11009,7 +11009,7 @@
         <v>19461</v>
       </c>
     </row>
-    <row r="206" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="206" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F206">
         <v>317.19</v>
       </c>
@@ -11020,7 +11020,7 @@
         <v>19511</v>
       </c>
     </row>
-    <row r="208" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="208" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F208">
         <v>317.19</v>
       </c>
@@ -11031,7 +11031,7 @@
         <v>19561</v>
       </c>
     </row>
-    <row r="210" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="210" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F210">
         <v>317.19</v>
       </c>
@@ -11042,7 +11042,7 @@
         <v>19611</v>
       </c>
     </row>
-    <row r="212" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="212" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F212">
         <v>317.19</v>
       </c>
@@ -11053,7 +11053,7 @@
         <v>19661</v>
       </c>
     </row>
-    <row r="214" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="214" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F214">
         <v>317.19</v>
       </c>
@@ -11064,7 +11064,7 @@
         <v>19712</v>
       </c>
     </row>
-    <row r="216" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="216" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F216">
         <v>317.19</v>
       </c>
@@ -11075,7 +11075,7 @@
         <v>19771</v>
       </c>
     </row>
-    <row r="218" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="218" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F218">
         <v>317.19</v>
       </c>
@@ -11086,7 +11086,7 @@
         <v>19821</v>
       </c>
     </row>
-    <row r="220" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="220" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F220">
         <v>317.19</v>
       </c>
@@ -11097,7 +11097,7 @@
         <v>19871</v>
       </c>
     </row>
-    <row r="222" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="222" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F222">
         <v>317.19</v>
       </c>
@@ -11108,7 +11108,7 @@
         <v>19921</v>
       </c>
     </row>
-    <row r="224" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="224" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F224">
         <v>317.19</v>
       </c>
@@ -11119,7 +11119,7 @@
         <v>19971</v>
       </c>
     </row>
-    <row r="226" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="226" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F226">
         <v>317.19</v>
       </c>
@@ -11130,7 +11130,7 @@
         <v>20021</v>
       </c>
     </row>
-    <row r="228" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="228" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F228">
         <v>317.19</v>
       </c>
@@ -11141,7 +11141,7 @@
         <v>20071</v>
       </c>
     </row>
-    <row r="230" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="230" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F230">
         <v>317.19</v>
       </c>
@@ -11152,7 +11152,7 @@
         <v>20121</v>
       </c>
     </row>
-    <row r="232" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="232" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F232">
         <v>317.19</v>
       </c>
@@ -11171,17 +11171,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06314498-3CF0-0A4A-8002-08331D734FA9}">
   <dimension ref="A1:H236"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.19921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.19921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -11189,7 +11189,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -11209,7 +11209,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>0</v>
       </c>
@@ -11229,7 +11229,7 @@
         <v>14441</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>0</v>
       </c>
@@ -11249,7 +11249,7 @@
         <v>14491</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>0</v>
       </c>
@@ -11269,7 +11269,7 @@
         <v>14541</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>-3.55</v>
       </c>
@@ -11289,7 +11289,7 @@
         <v>14592</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>-6.81</v>
       </c>
@@ -11309,7 +11309,7 @@
         <v>14651</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>-11.22</v>
       </c>
@@ -11329,7 +11329,7 @@
         <v>14701</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>-14.06</v>
       </c>
@@ -11349,7 +11349,7 @@
         <v>14751</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>-18.04</v>
       </c>
@@ -11369,7 +11369,7 @@
         <v>14801</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>-20.87</v>
       </c>
@@ -11389,7 +11389,7 @@
         <v>14851</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>-24.99</v>
       </c>
@@ -11409,7 +11409,7 @@
         <v>14901</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>-27.97</v>
       </c>
@@ -11429,7 +11429,7 @@
         <v>14951</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>-32.229999999999997</v>
       </c>
@@ -11449,7 +11449,7 @@
         <v>15001</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>-35.200000000000003</v>
       </c>
@@ -11469,7 +11469,7 @@
         <v>15051</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>-39.46</v>
       </c>
@@ -11489,7 +11489,7 @@
         <v>15101</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>-42.57</v>
       </c>
@@ -11509,7 +11509,7 @@
         <v>15151</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>-46.96</v>
       </c>
@@ -11529,7 +11529,7 @@
         <v>15201</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>-50.07</v>
       </c>
@@ -11549,7 +11549,7 @@
         <v>15251</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>-54.6</v>
       </c>
@@ -11569,7 +11569,7 @@
         <v>15301</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>-57.57</v>
       </c>
@@ -11589,7 +11589,7 @@
         <v>15351</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>-62.23</v>
       </c>
@@ -11609,7 +11609,7 @@
         <v>15401</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>-65.47</v>
       </c>
@@ -11629,7 +11629,7 @@
         <v>15451</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>-70.260000000000005</v>
       </c>
@@ -11649,7 +11649,7 @@
         <v>15501</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>-73.22</v>
       </c>
@@ -11669,7 +11669,7 @@
         <v>15551</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>-78</v>
       </c>
@@ -11689,7 +11689,7 @@
         <v>15601</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>-81.23</v>
       </c>
@@ -11709,7 +11709,7 @@
         <v>15651</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>-86.14</v>
       </c>
@@ -11729,7 +11729,7 @@
         <v>15702</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>-89.22</v>
       </c>
@@ -11749,7 +11749,7 @@
         <v>15761</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>-93.98</v>
       </c>
@@ -11769,7 +11769,7 @@
         <v>15811</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>-97.19</v>
       </c>
@@ -11789,7 +11789,7 @@
         <v>15861</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>-102.08</v>
       </c>
@@ -11809,7 +11809,7 @@
         <v>15911</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>-105.43</v>
       </c>
@@ -11829,7 +11829,7 @@
         <v>15961</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>-110.16</v>
       </c>
@@ -11849,7 +11849,7 @@
         <v>16011</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>-113.5</v>
       </c>
@@ -11869,7 +11869,7 @@
         <v>16061</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>-118.22</v>
       </c>
@@ -11889,7 +11889,7 @@
         <v>16111</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>-121.41</v>
       </c>
@@ -11909,7 +11909,7 @@
         <v>16161</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>-126.67</v>
       </c>
@@ -11929,7 +11929,7 @@
         <v>16211</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>-129.99</v>
       </c>
@@ -11949,7 +11949,7 @@
         <v>16261</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>-135.1</v>
       </c>
@@ -11969,7 +11969,7 @@
         <v>16311</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>-138.54</v>
       </c>
@@ -11989,7 +11989,7 @@
         <v>16361</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>-143.49</v>
       </c>
@@ -12009,7 +12009,7 @@
         <v>16411</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>-146.78</v>
       </c>
@@ -12029,7 +12029,7 @@
         <v>16461</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>-151.97999999999999</v>
       </c>
@@ -12049,7 +12049,7 @@
         <v>16512</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>-155.53</v>
       </c>
@@ -12069,7 +12069,7 @@
         <v>16571</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>-160.97999999999999</v>
       </c>
@@ -12089,7 +12089,7 @@
         <v>16621</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>-164.1</v>
       </c>
@@ -12109,7 +12109,7 @@
         <v>16671</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>-169.39</v>
       </c>
@@ -12129,7 +12129,7 @@
         <v>16721</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>-172.91</v>
       </c>
@@ -12149,7 +12149,7 @@
         <v>16771</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>-178.17</v>
       </c>
@@ -12169,7 +12169,7 @@
         <v>16821</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>-181.8</v>
       </c>
@@ -12189,7 +12189,7 @@
         <v>16871</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>-187.3</v>
       </c>
@@ -12209,7 +12209,7 @@
         <v>16921</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>-190.64</v>
       </c>
@@ -12229,7 +12229,7 @@
         <v>16971</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>-195.98</v>
       </c>
@@ -12249,7 +12249,7 @@
         <v>17021</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>-199.44</v>
       </c>
@@ -12269,7 +12269,7 @@
         <v>17071</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>-204.61</v>
       </c>
@@ -12289,7 +12289,7 @@
         <v>17121</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>-208.19</v>
       </c>
@@ -12309,7 +12309,7 @@
         <v>17171</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>-213.59</v>
       </c>
@@ -12329,7 +12329,7 @@
         <v>17221</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>-217.14</v>
       </c>
@@ -12349,7 +12349,7 @@
         <v>17271</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>-222.38</v>
       </c>
@@ -12369,7 +12369,7 @@
         <v>17321</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>-225.77</v>
       </c>
@@ -12389,7 +12389,7 @@
         <v>17371</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>-231.37</v>
       </c>
@@ -12409,7 +12409,7 @@
         <v>17421</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>-234.73</v>
       </c>
@@ -12429,7 +12429,7 @@
         <v>17471</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>-240.29</v>
       </c>
@@ -12449,7 +12449,7 @@
         <v>17521</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>-243.76</v>
       </c>
@@ -12469,7 +12469,7 @@
         <v>17571</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>-249.01</v>
       </c>
@@ -12489,7 +12489,7 @@
         <v>17622</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>-252.58</v>
       </c>
@@ -12509,7 +12509,7 @@
         <v>17681</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>-257.91000000000003</v>
       </c>
@@ -12529,7 +12529,7 @@
         <v>17731</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>-261.58</v>
       </c>
@@ -12549,7 +12549,7 @@
         <v>17781</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>-265.60000000000002</v>
       </c>
@@ -12569,7 +12569,7 @@
         <v>17831</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>-268.11</v>
       </c>
@@ -12589,7 +12589,7 @@
         <v>17881</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>-271.33999999999997</v>
       </c>
@@ -12609,7 +12609,7 @@
         <v>17931</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>-273.58</v>
       </c>
@@ -12629,7 +12629,7 @@
         <v>17981</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>-277.27999999999997</v>
       </c>
@@ -12649,7 +12649,7 @@
         <v>18031</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>-279.73</v>
       </c>
@@ -12669,7 +12669,7 @@
         <v>18081</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>-283.27</v>
       </c>
@@ -12689,7 +12689,7 @@
         <v>18131</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>-285.58</v>
       </c>
@@ -12709,7 +12709,7 @@
         <v>18181</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>-289.20999999999998</v>
       </c>
@@ -12729,7 +12729,7 @@
         <v>18231</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>-291.5</v>
       </c>
@@ -12749,7 +12749,7 @@
         <v>18281</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>-294.97000000000003</v>
       </c>
@@ -12769,7 +12769,7 @@
         <v>18331</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>-297.35000000000002</v>
       </c>
@@ -12789,7 +12789,7 @@
         <v>18381</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>-300.79000000000002</v>
       </c>
@@ -12809,7 +12809,7 @@
         <v>18432</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>-303.02</v>
       </c>
@@ -12829,7 +12829,7 @@
         <v>18491</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F166">
         <v>243.84</v>
       </c>
@@ -12840,7 +12840,7 @@
         <v>18541</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F168">
         <v>248.54</v>
       </c>
@@ -12851,7 +12851,7 @@
         <v>18591</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F170">
         <v>253.48</v>
       </c>
@@ -12862,7 +12862,7 @@
         <v>18641</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F172">
         <v>258.26</v>
       </c>
@@ -12873,7 +12873,7 @@
         <v>18691</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F174">
         <v>262.58</v>
       </c>
@@ -12884,7 +12884,7 @@
         <v>18741</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F176">
         <v>267.13</v>
       </c>
@@ -12895,7 +12895,7 @@
         <v>18791</v>
       </c>
     </row>
-    <row r="178" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="178" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F178">
         <v>271.89</v>
       </c>
@@ -12906,7 +12906,7 @@
         <v>18841</v>
       </c>
     </row>
-    <row r="180" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="180" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F180">
         <v>276.45999999999998</v>
       </c>
@@ -12917,7 +12917,7 @@
         <v>18891</v>
       </c>
     </row>
-    <row r="182" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="182" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F182">
         <v>281.10000000000002</v>
       </c>
@@ -12928,7 +12928,7 @@
         <v>18941</v>
       </c>
     </row>
-    <row r="184" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="184" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F184">
         <v>285.42</v>
       </c>
@@ -12939,7 +12939,7 @@
         <v>18991</v>
       </c>
     </row>
-    <row r="186" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="186" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F186">
         <v>289.64999999999998</v>
       </c>
@@ -12950,7 +12950,7 @@
         <v>19041</v>
       </c>
     </row>
-    <row r="188" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="188" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F188">
         <v>294.06</v>
       </c>
@@ -12961,7 +12961,7 @@
         <v>19091</v>
       </c>
     </row>
-    <row r="190" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="190" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F190">
         <v>298.25</v>
       </c>
@@ -12972,7 +12972,7 @@
         <v>19141</v>
       </c>
     </row>
-    <row r="192" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="192" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F192">
         <v>302.22000000000003</v>
       </c>
@@ -12983,7 +12983,7 @@
         <v>19191</v>
       </c>
     </row>
-    <row r="194" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="194" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F194">
         <v>306.19</v>
       </c>
@@ -12994,7 +12994,7 @@
         <v>19241</v>
       </c>
     </row>
-    <row r="196" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="196" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F196">
         <v>309.70999999999998</v>
       </c>
@@ -13005,7 +13005,7 @@
         <v>19291</v>
       </c>
     </row>
-    <row r="198" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="198" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F198">
         <v>311.83999999999997</v>
       </c>
@@ -13016,7 +13016,7 @@
         <v>19341</v>
       </c>
     </row>
-    <row r="200" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="200" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F200">
         <v>312.05</v>
       </c>
@@ -13027,7 +13027,7 @@
         <v>19391</v>
       </c>
     </row>
-    <row r="202" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="202" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F202">
         <v>312.05</v>
       </c>
@@ -13038,7 +13038,7 @@
         <v>19441</v>
       </c>
     </row>
-    <row r="204" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="204" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F204">
         <v>312.05</v>
       </c>
@@ -13049,7 +13049,7 @@
         <v>19491</v>
       </c>
     </row>
-    <row r="206" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="206" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F206">
         <v>312.05</v>
       </c>
@@ -13060,7 +13060,7 @@
         <v>19542</v>
       </c>
     </row>
-    <row r="208" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="208" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F208">
         <v>312.05</v>
       </c>
@@ -13071,7 +13071,7 @@
         <v>19601</v>
       </c>
     </row>
-    <row r="210" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="210" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F210">
         <v>312.05</v>
       </c>
@@ -13082,7 +13082,7 @@
         <v>19651</v>
       </c>
     </row>
-    <row r="212" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="212" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F212">
         <v>312.05</v>
       </c>
@@ -13093,7 +13093,7 @@
         <v>19701</v>
       </c>
     </row>
-    <row r="214" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="214" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F214">
         <v>312.05</v>
       </c>
@@ -13104,7 +13104,7 @@
         <v>19751</v>
       </c>
     </row>
-    <row r="216" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="216" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F216">
         <v>312.05</v>
       </c>
@@ -13115,7 +13115,7 @@
         <v>19801</v>
       </c>
     </row>
-    <row r="218" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="218" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F218">
         <v>312.05</v>
       </c>
@@ -13126,7 +13126,7 @@
         <v>19851</v>
       </c>
     </row>
-    <row r="220" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="220" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F220">
         <v>312.05</v>
       </c>
@@ -13137,7 +13137,7 @@
         <v>19901</v>
       </c>
     </row>
-    <row r="222" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="222" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F222">
         <v>312.05</v>
       </c>
@@ -13148,7 +13148,7 @@
         <v>19951</v>
       </c>
     </row>
-    <row r="224" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="224" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F224">
         <v>312.05</v>
       </c>
@@ -13159,7 +13159,7 @@
         <v>20001</v>
       </c>
     </row>
-    <row r="226" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="226" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F226">
         <v>312.05</v>
       </c>
@@ -13170,7 +13170,7 @@
         <v>20051</v>
       </c>
     </row>
-    <row r="228" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="228" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F228">
         <v>312.05</v>
       </c>
@@ -13181,7 +13181,7 @@
         <v>20101</v>
       </c>
     </row>
-    <row r="230" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="230" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F230">
         <v>312.05</v>
       </c>
@@ -13192,7 +13192,7 @@
         <v>20151</v>
       </c>
     </row>
-    <row r="232" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="232" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F232">
         <v>312.05</v>
       </c>
@@ -13203,7 +13203,7 @@
         <v>20201</v>
       </c>
     </row>
-    <row r="234" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="234" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F234">
         <v>312.05</v>
       </c>
@@ -13214,7 +13214,7 @@
         <v>20251</v>
       </c>
     </row>
-    <row r="236" spans="6:8" x14ac:dyDescent="0.2">
+    <row r="236" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F236">
         <v>312.05</v>
       </c>
